--- a/data/IOmaterial/试验颜色对照表.xlsx
+++ b/data/IOmaterial/试验颜色对照表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10980"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>红</t>
   </si>
@@ -73,6 +73,12 @@
     <t>白棕</t>
   </si>
   <si>
+    <t>光电限位</t>
+  </si>
+  <si>
+    <t>以前的X4</t>
+  </si>
+  <si>
     <t>a+</t>
   </si>
   <si>
@@ -95,6 +101,15 @@
   </si>
   <si>
     <t>地</t>
+  </si>
+  <si>
+    <t>绝缘线</t>
+  </si>
+  <si>
+    <t>驱动器io口</t>
+  </si>
+  <si>
+    <t>现在的X4</t>
   </si>
 </sst>
 </file>
@@ -1025,8 +1040,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <dimension ref="B1:F11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" t="s">
@@ -1102,14 +1117,20 @@
       </c>
     </row>
     <row r="6" spans="2:6">
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
       <c r="D6">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:6">
@@ -1117,10 +1138,10 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="2:6">
@@ -1128,7 +1149,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
@@ -1139,10 +1160,10 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -1150,7 +1171,18 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1164,7 +1196,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1176,7 +1208,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
